--- a/Config/Datas/Tables/b_Boss遭遇_BossEncounterConfig.xlsx
+++ b/Config/Datas/Tables/b_Boss遭遇_BossEncounterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbBossEncounter" sheetId="1" r:id="Rf0d96bf18865462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbBossEncounter" sheetId="1" r:id="R071319e290444fa3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,6 +495,23 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>40101</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>劫狱执印者</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
